--- a/GUT/GUT-modelo.xlsx
+++ b/GUT/GUT-modelo.xlsx
@@ -298,7 +298,7 @@
     <t xml:space="preserve">Exemplo 2 - Compras</t>
   </si>
   <si>
-    <t xml:space="preserve">Matriz preenchida com sete problemas de uma área, incluindo um empate.</t>
+    <t xml:space="preserve">Matriz preenchida com sete problemas da área de compras de uma distribuidora, incluindo um empate.</t>
   </si>
   <si>
     <t xml:space="preserve">Regras e premissas do modelo</t>
@@ -844,13 +844,13 @@
     <t xml:space="preserve">Margem do delivery caiu com o aumento da taxa do aplicativo</t>
   </si>
   <si>
-    <t xml:space="preserve">Erros de sabor ou de tamanho em 3% dos pedidos</t>
+    <t xml:space="preserve">Erros de sabor ou de tamanho em 2% dos pedidos</t>
   </si>
   <si>
     <t xml:space="preserve">Reclamação</t>
   </si>
   <si>
-    <t xml:space="preserve">Desperdício de ingredientes acima de 8% do consumo</t>
+    <t xml:space="preserve">Desperdício de insumos em 3,9% do custo comprado</t>
   </si>
   <si>
     <t xml:space="preserve">Licença sanitária vence em 45 dias</t>
@@ -898,7 +898,7 @@
     <t xml:space="preserve">Gerente de Suprimentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Suprimentos</t>
+    <t xml:space="preserve">Distribuidora de materiais elétricos · Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Equipe de compras</t>
@@ -1700,11 +1700,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="0"/>
-        <c:axId val="91850086"/>
-        <c:axId val="79301096"/>
+        <c:axId val="53864313"/>
+        <c:axId val="69234429"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91850086"/>
+        <c:axId val="53864313"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1736,7 +1736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79301096"/>
+        <c:crossAx val="69234429"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1744,7 +1744,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79301096"/>
+        <c:axId val="69234429"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="125"/>
@@ -1785,7 +1785,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91850086"/>
+        <c:crossAx val="53864313"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
@@ -5432,16 +5432,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H6:H20" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Código do problema na aba GUT" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C6:C20" type="list">
       <formula1>"P1,P2,P3,P4,P5,P6,P7,P8,P9,P10,P11,P12,P13,P14,P15,P16,P17,P18,P19,P20"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I6:I20" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H6:H20" type="date">
+      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7223,7 +7223,7 @@
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="43" t="n">
-        <v>46294</v>
+        <v>46171</v>
       </c>
       <c r="J5" s="43"/>
       <c r="K5" s="43"/>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="48" t="n">
-        <v>46304</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="48" t="n">
-        <v>46374</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="48" t="n">
-        <v>46325</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="48" t="n">
-        <v>46311</v>
+        <v>46189</v>
       </c>
     </row>
   </sheetData>

--- a/GUT/GUT-modelo.xlsx
+++ b/GUT/GUT-modelo.xlsx
@@ -1700,11 +1700,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="0"/>
-        <c:axId val="53864313"/>
-        <c:axId val="69234429"/>
+        <c:axId val="8985635"/>
+        <c:axId val="63232850"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53864313"/>
+        <c:axId val="8985635"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1736,7 +1736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69234429"/>
+        <c:crossAx val="63232850"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1744,7 +1744,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69234429"/>
+        <c:axId val="63232850"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="125"/>
@@ -1785,7 +1785,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53864313"/>
+        <c:crossAx val="8985635"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="25"/>
